--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T16:48:59+00:00</t>
+    <t>2026-04-25T16:59:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T16:59:12+00:00</t>
+    <t>2026-04-25T17:20:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T17:20:31+00:00</t>
+    <t>2026-04-25T17:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/fhirpot-audit-event</t>
+    <t>https://constir1.github.io/ATTCK2FHIR/StructureDefinition/fhirpot-audit-event</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T17:34:35+00:00</t>
+    <t>2026-04-25T21:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ATTCK2FHIR IG</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ATTCK2FHIR IG (https://constir1.github.io/ATTCK2FHIR)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:04:27+00:00</t>
+    <t>2026-04-25T21:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:17:05+00:00</t>
+    <t>2026-04-25T21:19:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:19:40+00:00</t>
+    <t>2026-04-25T21:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T21:21:24+00:00</t>
+    <t>2026-04-26T14:57:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T14:57:42+00:00</t>
+    <t>2026-04-26T15:13:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T15:13:50+00:00</t>
+    <t>2026-04-26T15:44:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.3</t>
+    <t>0.0.04</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T15:44:08+00:00</t>
+    <t>2026-04-26T15:55:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.04</t>
+    <t>0.0.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-26T15:55:31+00:00</t>
+    <t>2026-04-26T20:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.6</t>
+    <t>0.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:02:20+00:00</t>
+    <t>2026-05-14T08:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.7</t>
+    <t>0.0.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:13:13+00:00</t>
+    <t>2026-05-14T10:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>AuditEvent profile for FHIR honeypot detections with MITRE ATT&amp;CK and OWASP</t>
+    <t>AuditEvent profile for FHIR honeypot detections, classifying events with MITRE ATT&amp;CK tactics, techniques, and (optionally) subtechniques.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -472,60 +472,103 @@
 </t>
   </si>
   <si>
-    <t>Type/identifier of event</t>
-  </si>
-  <si>
-    <t>Identifier for a family of the event.  For example, a menu item, program, rule, policy, function code, application name or URL. It identifies the performed function.</t>
+    <t>MITRE ATT&amp;CK Tactic associated with the technique</t>
+  </si>
+  <si>
+    <t>The MITRE ATT&amp;CK tactic this event maps to. SHALL be one of the tactic codes listed on the technique referenced in AuditEvent.subtype[technique] via the MITRE-ATTCK-Techniques CodeSystem's `tactic` property. This profile does not enforce the cross-element linkage with a FHIRPath invariant because R4 cannot portably read CodeSystem properties from FHIRPath; implementers are responsible for the linkage.</t>
   </si>
   <si>
     <t>This identifies the performed function. For "Execute" Event Action Code audit records, this identifies the application function performed.</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Tactics</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>.code (type, subtype and action are pre-coordinated or sent as translations)</t>
+  </si>
+  <si>
+    <t>EventId</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>AuditEvent.subtype</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>More specific type/id for the event</t>
+  </si>
+  <si>
+    <t>Identifier for the category of event.</t>
+  </si>
+  <si>
+    <t>This field enables queries of messages by implementation-defined event categories.</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>Type of event.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/audit-event-type|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>.code (type, subtype and action are pre-coordinated or sent as translations)</t>
-  </si>
-  <si>
-    <t>EventId</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>AuditEvent.subtype</t>
-  </si>
-  <si>
-    <t>More specific type/id for the event</t>
-  </si>
-  <si>
-    <t>Identifier for the category of event.</t>
-  </si>
-  <si>
-    <t>This field enables queries of messages by implementation-defined event categories.</t>
-  </si>
-  <si>
     <t>Sub-type of event.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/audit-event-sub-type|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>First entry is the MITRE ATT&amp;CK technique; an optional second entry refines it to a subtechnique of that technique.</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>EventTypeCode</t>
   </si>
   <si>
+    <t>AuditEvent.subtype:technique</t>
+  </si>
+  <si>
+    <t>technique</t>
+  </si>
+  <si>
+    <t>MITRE ATT&amp;CK Technique (parent)</t>
+  </si>
+  <si>
+    <t>The MITRE ATT&amp;CK parent technique (e.g. T1037). Exactly one is required per event.</t>
+  </si>
+  <si>
+    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Parent-Techniques</t>
+  </si>
+  <si>
+    <t>AuditEvent.subtype:subtechnique</t>
+  </si>
+  <si>
+    <t>subtechnique</t>
+  </si>
+  <si>
+    <t>MITRE ATT&amp;CK Subtechnique (optional refinement)</t>
+  </si>
+  <si>
+    <t>An optional MITRE ATT&amp;CK subtechnique (e.g. T1037.004) that refines subtype[technique]. SHALL be a subtechnique whose `parentTechnique` property points to the code in subtype[technique] — not enforced here for the same reason given on `type`.</t>
+  </si>
+  <si>
+    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Subtechniques</t>
+  </si>
+  <si>
     <t>AuditEvent.action</t>
   </si>
   <si>
@@ -536,9 +579,6 @@
   </si>
   <si>
     <t>This broadly indicates what kind of action was done on the AuditEvent.entity by the AuditEvent.agent.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>Indicator for type of action performed during the event that generated the event.</t>
@@ -671,7 +711,10 @@
     <t>Use AuditEvent.agent.purposeOfUse when you know that it is specific to the agent, otherwise use AuditEvent.purposeOfEvent. For example, during a machine-to-machine transfer it might not be obvious to the audit system who caused the event, but it does know why.</t>
   </si>
   <si>
-    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Tactics</t>
+    <t>The reason the activity took place.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1090,12 +1133,6 @@
   </si>
   <si>
     <t>Use AuditEvent.agent.purposeOfUse when you know that is specific to the agent, otherwise use AuditEvent.purposeOfEvent. For example, during a machine-to-machine transfer it might not be obvious to the audit system who caused the event, but it does know why.</t>
-  </si>
-  <si>
-    <t>The reason the activity took place.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
   </si>
   <si>
     <t>*.reasonCode [ActHealthInformationPurposeOfUseReason codes/v:PurposeOfUse
@@ -1803,12 +1840,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP63"/>
+  <dimension ref="A1:AP65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.1875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.1875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="11.546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1831,10 +1868,10 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="65.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.5078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="91.64453125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3122,11 +3159,9 @@
       <c r="X11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Y11" t="s" s="2">
+      <c r="Y11" s="2"/>
+      <c r="Z11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>18</v>
@@ -3159,19 +3194,19 @@
         <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>18</v>
@@ -3179,10 +3214,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3190,10 +3225,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>18</v>
@@ -3240,31 +3275,31 @@
         <v>18</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3282,13 +3317,13 @@
         <v>18</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>18</v>
@@ -3299,18 +3334,20 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>88</v>
@@ -3325,17 +3362,17 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>18</v>
@@ -3360,13 +3397,11 @@
         <v>18</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>18</v>
@@ -3384,13 +3419,13 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>18</v>
@@ -3402,13 +3437,13 @@
         <v>18</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>18</v>
@@ -3419,12 +3454,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>18</v>
       </c>
@@ -3442,21 +3479,21 @@
         <v>18</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="O14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>18</v>
       </c>
@@ -3480,13 +3517,11 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>18</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -3504,13 +3539,13 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>18</v>
@@ -3519,30 +3554,30 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>178</v>
+        <v>18</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>183</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3550,7 +3585,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>88</v>
@@ -3565,19 +3600,17 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>18</v>
@@ -3602,13 +3635,13 @@
         <v>18</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>18</v>
+        <v>183</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -3626,10 +3659,10 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>88</v>
@@ -3644,27 +3677,27 @@
         <v>18</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3684,19 +3717,19 @@
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3722,13 +3755,13 @@
         <v>18</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -3746,7 +3779,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3761,30 +3794,30 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>18</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3792,7 +3825,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>88</v>
@@ -3807,16 +3840,20 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
       </c>
@@ -3864,10 +3901,10 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>88</v>
@@ -3882,19 +3919,19 @@
         <v>18</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -3913,7 +3950,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>18</v>
@@ -3925,16 +3962,16 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3962,9 +3999,11 @@
       <c r="X18" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Y18" s="2"/>
+      <c r="Y18" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
@@ -3988,7 +4027,7 @@
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>18</v>
@@ -3997,42 +4036,42 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>155</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>218</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G19" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="H19" t="s" s="2">
         <v>18</v>
       </c>
@@ -4040,23 +4079,19 @@
         <v>18</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>18</v>
       </c>
@@ -4104,13 +4139,13 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH19" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>18</v>
@@ -4119,30 +4154,30 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>226</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4153,7 +4188,7 @@
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>18</v>
@@ -4162,18 +4197,20 @@
         <v>18</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4198,13 +4235,13 @@
         <v>18</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>18</v>
+        <v>226</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -4222,53 +4259,53 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>18</v>
+        <v>227</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>18</v>
+        <v>230</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>18</v>
+        <v>231</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>18</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>133</v>
+        <v>234</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>78</v>
@@ -4283,18 +4320,20 @@
         <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>235</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>135</v>
+        <v>236</v>
       </c>
       <c r="M21" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="N21" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
       </c>
@@ -4342,10 +4381,10 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>78</v>
@@ -4354,69 +4393,65 @@
         <v>18</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>18</v>
+        <v>242</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>18</v>
+        <v>243</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>18</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>18</v>
       </c>
@@ -4464,25 +4499,25 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>18</v>
@@ -4499,21 +4534,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>18</v>
@@ -4525,15 +4560,17 @@
         <v>18</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>246</v>
+        <v>135</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4558,13 +4595,13 @@
         <v>18</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>248</v>
+        <v>18</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>249</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>18</v>
@@ -4582,49 +4619,49 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>253</v>
+        <v>18</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>254</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>18</v>
+        <v>255</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4637,13 +4674,13 @@
         <v>18</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>256</v>
@@ -4652,10 +4689,10 @@
         <v>257</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>258</v>
+        <v>137</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>259</v>
+        <v>143</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4680,13 +4717,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>261</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>262</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -4704,7 +4741,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4716,37 +4753,37 @@
         <v>18</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>263</v>
+        <v>131</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>253</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>264</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>266</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4762,23 +4799,19 @@
         <v>18</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>267</v>
+        <v>221</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>18</v>
       </c>
@@ -4802,13 +4835,13 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>18</v>
+        <v>262</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
@@ -4826,7 +4859,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4841,30 +4874,30 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4875,7 +4908,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -4887,17 +4920,19 @@
         <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -4922,13 +4957,13 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>18</v>
+        <v>274</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>18</v>
+        <v>275</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>18</v>
+        <v>276</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
@@ -4946,13 +4981,13 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>18</v>
@@ -4964,31 +4999,31 @@
         <v>18</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>18</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>18</v>
+        <v>280</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5004,20 +5039,22 @@
         <v>18</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>202</v>
+        <v>281</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5066,7 +5103,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5081,7 +5118,7 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>18</v>
+        <v>286</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>287</v>
@@ -5090,21 +5127,21 @@
         <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>18</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5112,7 +5149,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>
@@ -5124,20 +5161,18 @@
         <v>18</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>290</v>
+        <v>215</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N28" t="s" s="2">
         <v>293</v>
       </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>294</v>
       </c>
@@ -5188,10 +5223,10 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>88</v>
@@ -5212,10 +5247,10 @@
         <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>18</v>
+        <v>289</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>18</v>
@@ -5249,16 +5284,18 @@
         <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5321,30 +5358,30 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AM29" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>305</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5352,10 +5389,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
@@ -5364,22 +5401,22 @@
         <v>18</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>18</v>
@@ -5428,13 +5465,13 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>18</v>
@@ -5446,27 +5483,27 @@
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>313</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5489,18 +5526,16 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>146</v>
+        <v>312</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>317</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>18</v>
       </c>
@@ -5524,13 +5559,13 @@
         <v>18</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>318</v>
+        <v>18</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>319</v>
+        <v>18</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>18</v>
@@ -5548,7 +5583,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5563,30 +5598,30 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>18</v>
+        <v>315</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>321</v>
+        <v>18</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>18</v>
+        <v>318</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>18</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5597,7 +5632,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>18</v>
@@ -5609,16 +5644,20 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>221</v>
+        <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>18</v>
       </c>
@@ -5666,13 +5705,13 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>18</v>
@@ -5687,24 +5726,24 @@
         <v>325</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>18</v>
+        <v>326</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>18</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5727,16 +5766,18 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>233</v>
+        <v>329</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>234</v>
+        <v>330</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>18</v>
       </c>
@@ -5760,13 +5801,13 @@
         <v>18</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>18</v>
+        <v>332</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>18</v>
+        <v>333</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>18</v>
@@ -5784,7 +5825,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>235</v>
+        <v>328</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5796,19 +5837,19 @@
         <v>18</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>236</v>
+        <v>334</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>18</v>
+        <v>335</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>18</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>18</v>
@@ -5819,21 +5860,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>18</v>
@@ -5845,17 +5886,15 @@
         <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>134</v>
+        <v>235</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>135</v>
+        <v>337</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>18</v>
@@ -5904,31 +5943,31 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>239</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>236</v>
+        <v>339</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>18</v>
+        <v>317</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -5939,46 +5978,42 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>18</v>
       </c>
@@ -6026,25 +6061,25 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>18</v>
@@ -6061,21 +6096,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>18</v>
@@ -6087,20 +6122,18 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>202</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>330</v>
+        <v>135</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>331</v>
+        <v>252</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>18</v>
       </c>
@@ -6148,34 +6181,34 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>334</v>
+        <v>250</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>303</v>
+        <v>18</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>336</v>
+        <v>18</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>18</v>
@@ -6183,43 +6216,45 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>18</v>
+        <v>255</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>340</v>
+        <v>143</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -6244,13 +6279,13 @@
         <v>18</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>341</v>
+        <v>18</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>342</v>
+        <v>18</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>18</v>
@@ -6268,31 +6303,31 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>258</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>334</v>
+        <v>131</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>343</v>
+        <v>18</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>303</v>
+        <v>18</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>18</v>
@@ -6303,10 +6338,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6317,7 +6352,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>18</v>
@@ -6329,18 +6364,20 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>18</v>
       </c>
@@ -6364,13 +6401,13 @@
         <v>18</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>348</v>
+        <v>18</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>349</v>
+        <v>18</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>18</v>
@@ -6388,13 +6425,13 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>18</v>
@@ -6406,16 +6443,16 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>18</v>
@@ -6423,10 +6460,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6434,7 +6471,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
@@ -6449,19 +6486,17 @@
         <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>221</v>
+        <v>108</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6486,13 +6521,13 @@
         <v>18</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>18</v>
+        <v>355</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>18</v>
+        <v>356</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>18</v>
@@ -6510,10 +6545,10 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>88</v>
@@ -6528,13 +6563,13 @@
         <v>18</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>359</v>
+        <v>317</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6545,10 +6580,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6559,7 +6594,7 @@
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>18</v>
@@ -6571,15 +6606,17 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>233</v>
+        <v>359</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6604,13 +6641,13 @@
         <v>18</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>18</v>
+        <v>226</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>18</v>
@@ -6628,34 +6665,34 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>235</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>236</v>
+        <v>362</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>18</v>
+        <v>230</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>18</v>
+        <v>363</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>18</v>
@@ -6663,21 +6700,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>18</v>
@@ -6689,18 +6726,20 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>235</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>135</v>
+        <v>365</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>238</v>
+        <v>366</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>18</v>
       </c>
@@ -6748,31 +6787,31 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>239</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>236</v>
+        <v>369</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>18</v>
+        <v>370</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>18</v>
+        <v>371</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -6783,46 +6822,42 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>18</v>
       </c>
@@ -6870,25 +6905,25 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>18</v>
@@ -6905,21 +6940,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>18</v>
@@ -6931,18 +6966,18 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>202</v>
+        <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>364</v>
+        <v>135</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>18</v>
       </c>
@@ -6990,31 +7025,31 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>363</v>
+        <v>253</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>367</v>
+        <v>250</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>368</v>
+        <v>18</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>359</v>
+        <v>18</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -7025,43 +7060,45 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>370</v>
+        <v>255</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>267</v>
+        <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>371</v>
+        <v>256</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>373</v>
+        <v>143</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -7110,31 +7147,31 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>369</v>
+        <v>258</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>273</v>
+        <v>131</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>374</v>
+        <v>18</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>359</v>
+        <v>18</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7159,7 +7196,7 @@
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>18</v>
@@ -7171,7 +7208,7 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>376</v>
@@ -7206,13 +7243,13 @@
         <v>18</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>379</v>
+        <v>18</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>380</v>
+        <v>18</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>18</v>
@@ -7236,7 +7273,7 @@
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>18</v>
@@ -7248,13 +7285,13 @@
         <v>18</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7265,21 +7302,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>18</v>
@@ -7288,22 +7325,20 @@
         <v>18</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>18</v>
@@ -7352,45 +7387,45 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>389</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>390</v>
+        <v>287</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>156</v>
+        <v>371</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>392</v>
+        <v>18</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>393</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7401,7 +7436,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>18</v>
@@ -7413,16 +7448,18 @@
         <v>18</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>233</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>234</v>
+        <v>389</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
       </c>
@@ -7446,13 +7483,13 @@
         <v>18</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>18</v>
+        <v>391</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>18</v>
+        <v>392</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>18</v>
@@ -7470,31 +7507,31 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>235</v>
+        <v>387</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>236</v>
+        <v>393</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>18</v>
+        <v>394</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>18</v>
+        <v>371</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>18</v>
@@ -7512,7 +7549,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>133</v>
+        <v>396</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7531,18 +7568,20 @@
         <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>134</v>
+        <v>235</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>135</v>
+        <v>397</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>238</v>
+        <v>398</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
       </c>
@@ -7590,7 +7629,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>239</v>
+        <v>395</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7602,69 +7641,65 @@
         <v>18</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>139</v>
+        <v>401</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>236</v>
+        <v>402</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>18</v>
+        <v>403</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>18</v>
+        <v>404</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>18</v>
+        <v>405</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>18</v>
       </c>
@@ -7712,25 +7747,25 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>18</v>
@@ -7747,21 +7782,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>18</v>
@@ -7770,18 +7805,20 @@
         <v>18</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>398</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>399</v>
+        <v>135</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>18</v>
@@ -7830,80 +7867,80 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>397</v>
+        <v>253</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>401</v>
+        <v>18</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>402</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>18</v>
+        <v>255</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>404</v>
+        <v>256</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>405</v>
+        <v>257</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>406</v>
+        <v>137</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>407</v>
+        <v>143</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -7928,13 +7965,13 @@
         <v>18</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>408</v>
+        <v>18</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>409</v>
+        <v>18</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>18</v>
@@ -7952,45 +7989,45 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>403</v>
+        <v>258</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>410</v>
+        <v>131</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>411</v>
+        <v>18</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>412</v>
+        <v>18</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>413</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8010,21 +8047,19 @@
         <v>18</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>417</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>18</v>
       </c>
@@ -8048,13 +8083,13 @@
         <v>18</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>418</v>
+        <v>18</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>419</v>
+        <v>18</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>18</v>
@@ -8072,7 +8107,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8090,27 +8125,27 @@
         <v>18</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>420</v>
+        <v>287</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>422</v>
+        <v>155</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>423</v>
+        <v>18</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>18</v>
+        <v>414</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8136,16 +8171,16 @@
         <v>146</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>18</v>
@@ -8170,13 +8205,13 @@
         <v>18</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>18</v>
@@ -8194,7 +8229,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8212,27 +8247,27 @@
         <v>18</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>422</v>
+        <v>155</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8243,7 +8278,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>18</v>
@@ -8258,16 +8293,14 @@
         <v>146</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>18</v>
@@ -8292,13 +8325,13 @@
         <v>18</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>18</v>
@@ -8316,13 +8349,13 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>18</v>
@@ -8334,16 +8367,16 @@
         <v>18</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>18</v>
+        <v>435</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>18</v>
@@ -8351,10 +8384,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8374,22 +8407,22 @@
         <v>18</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>18</v>
@@ -8414,13 +8447,13 @@
         <v>18</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>18</v>
+        <v>438</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>18</v>
+        <v>441</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>18</v>
@@ -8438,7 +8471,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8447,7 +8480,7 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>447</v>
+        <v>18</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>100</v>
@@ -8456,27 +8489,27 @@
         <v>18</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>18</v>
+        <v>444</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8487,7 +8520,7 @@
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>18</v>
@@ -8499,17 +8532,19 @@
         <v>18</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
@@ -8534,13 +8569,13 @@
         <v>18</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>18</v>
+        <v>450</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>18</v>
+        <v>451</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>18</v>
@@ -8558,13 +8593,13 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>18</v>
@@ -8576,13 +8611,13 @@
         <v>18</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>18</v>
@@ -8593,10 +8628,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8619,19 +8654,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8680,7 +8715,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8689,7 +8724,7 @@
         <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>100</v>
@@ -8698,16 +8733,16 @@
         <v>18</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>18</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>18</v>
@@ -8715,10 +8750,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8729,7 +8764,7 @@
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>18</v>
@@ -8741,17 +8776,17 @@
         <v>18</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -8800,13 +8835,13 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>18</v>
@@ -8818,13 +8853,13 @@
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>18</v>
@@ -8835,10 +8870,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8858,19 +8893,23 @@
         <v>18</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>202</v>
+        <v>469</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>233</v>
+        <v>470</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
       </c>
@@ -8918,7 +8957,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>235</v>
+        <v>468</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8927,22 +8966,22 @@
         <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>18</v>
+        <v>459</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>236</v>
+        <v>474</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>18</v>
+        <v>475</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>18</v>
+        <v>434</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -8953,14 +8992,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8979,18 +9018,18 @@
         <v>18</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>235</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>135</v>
+        <v>477</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
       </c>
@@ -9038,7 +9077,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>239</v>
+        <v>476</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -9050,19 +9089,19 @@
         <v>18</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>236</v>
+        <v>480</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>18</v>
+        <v>481</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>18</v>
+        <v>434</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>18</v>
@@ -9073,46 +9112,42 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>18</v>
       </c>
@@ -9160,25 +9195,25 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>18</v>
@@ -9195,21 +9230,21 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>18</v>
@@ -9221,15 +9256,17 @@
         <v>18</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>202</v>
+        <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>474</v>
+        <v>135</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>18</v>
@@ -9278,31 +9315,31 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>473</v>
+        <v>253</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>381</v>
+        <v>250</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>476</v>
+        <v>18</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>422</v>
+        <v>18</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9313,45 +9350,45 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>18</v>
+        <v>255</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>478</v>
+        <v>134</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>479</v>
+        <v>256</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>480</v>
+        <v>257</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>481</v>
+        <v>137</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>482</v>
+        <v>143</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>18</v>
@@ -9400,36 +9437,276 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>477</v>
+        <v>258</v>
       </c>
       <c r="AG63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AH63" t="s" s="2">
+      <c r="G64" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AI63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
+      <c r="H64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP63" t="s" s="2">
+      <c r="AK64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>18</v>
       </c>
     </row>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.8</t>
+    <t>0.0.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T10:01:26+00:00</t>
+    <t>2026-05-14T18:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2440" uniqueCount="483">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.9</t>
+    <t>0.0.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T18:17:12+00:00</t>
+    <t>2026-05-15T18:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -508,65 +508,19 @@
     <t>2</t>
   </si>
   <si>
-    <t>More specific type/id for the event</t>
-  </si>
-  <si>
-    <t>Identifier for the category of event.</t>
+    <t>MITRE ATT&amp;CK Technique (parent), with optional subtechnique refinement</t>
+  </si>
+  <si>
+    <t>1..2 MITRE ATT&amp;CK technique codes. By convention the first entry is the parent technique (e.g. T1037) and the optional second entry is a subtechnique that refines it (e.g. T1037.004). This profile does not enforce slot order or the parent-subtechnique linkage at the FHIRPath layer because R4 discriminators cannot express ValueSet-based slicing; implementers are responsible for the ordering and the linkage.</t>
   </si>
   <si>
     <t>This field enables queries of messages by implementation-defined event categories.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Sub-type of event.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/audit-event-sub-type|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>First entry is the MITRE ATT&amp;CK technique; an optional second entry refines it to a subtechnique of that technique.</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Techniques</t>
   </si>
   <si>
     <t>EventTypeCode</t>
-  </si>
-  <si>
-    <t>AuditEvent.subtype:technique</t>
-  </si>
-  <si>
-    <t>technique</t>
-  </si>
-  <si>
-    <t>MITRE ATT&amp;CK Technique (parent)</t>
-  </si>
-  <si>
-    <t>The MITRE ATT&amp;CK parent technique (e.g. T1037). Exactly one is required per event.</t>
-  </si>
-  <si>
-    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Parent-Techniques</t>
-  </si>
-  <si>
-    <t>AuditEvent.subtype:subtechnique</t>
-  </si>
-  <si>
-    <t>subtechnique</t>
-  </si>
-  <si>
-    <t>MITRE ATT&amp;CK Subtechnique (optional refinement)</t>
-  </si>
-  <si>
-    <t>An optional MITRE ATT&amp;CK subtechnique (e.g. T1037.004) that refines subtype[technique]. SHALL be a subtechnique whose `parentTechnique` property points to the code in subtype[technique] — not enforced here for the same reason given on `type`.</t>
-  </si>
-  <si>
-    <t>https://constir1.github.io/ATTCK2FHIR/ValueSet/MITRE-ATTCK-Subtechniques</t>
   </si>
   <si>
     <t>AuditEvent.action</t>
@@ -709,6 +663,9 @@
   </si>
   <si>
     <t>Use AuditEvent.agent.purposeOfUse when you know that it is specific to the agent, otherwise use AuditEvent.purposeOfEvent. For example, during a machine-to-machine transfer it might not be obvious to the audit system who caused the event, but it does know why.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>The reason the activity took place.</t>
@@ -1840,12 +1797,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP65"/>
+  <dimension ref="A1:AP63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.1875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.1875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1868,10 +1825,10 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="65.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.5078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.8046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="91.64453125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3275,28 +3232,26 @@
         <v>18</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Y12" s="2"/>
+      <c r="Z12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="Y12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="AA12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>157</v>
@@ -3320,7 +3275,7 @@
         <v>153</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>155</v>
@@ -3334,20 +3289,18 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>18</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>88</v>
@@ -3362,17 +3315,17 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>18</v>
@@ -3399,9 +3352,11 @@
       <c r="X13" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Y13" s="2"/>
+      <c r="Y13" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>18</v>
@@ -3419,13 +3374,13 @@
         <v>18</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>18</v>
@@ -3440,7 +3395,7 @@
         <v>153</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>155</v>
@@ -3454,14 +3409,12 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>18</v>
       </c>
@@ -3479,21 +3432,21 @@
         <v>18</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>18</v>
       </c>
@@ -3517,11 +3470,13 @@
         <v>18</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>18</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>18</v>
@@ -3539,13 +3494,13 @@
         <v>18</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>18</v>
@@ -3554,30 +3509,30 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>18</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3585,7 +3540,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>88</v>
@@ -3600,17 +3555,19 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="O15" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>18</v>
@@ -3635,13 +3592,13 @@
         <v>18</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>184</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>18</v>
@@ -3659,10 +3616,10 @@
         <v>18</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>88</v>
@@ -3677,27 +3634,27 @@
         <v>18</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>18</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3717,19 +3674,19 @@
         <v>18</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3755,13 +3712,13 @@
         <v>18</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -3779,7 +3736,7 @@
         <v>18</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3794,30 +3751,30 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>196</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3825,7 +3782,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>88</v>
@@ -3840,20 +3797,16 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O17" t="s" s="2">
         <v>202</v>
       </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>18</v>
       </c>
@@ -3901,10 +3854,10 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>88</v>
@@ -3922,24 +3875,24 @@
         <v>203</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>155</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>18</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>206</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3950,7 +3903,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>18</v>
@@ -3962,16 +3915,16 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3997,13 +3950,13 @@
         <v>18</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>18</v>
@@ -4021,13 +3974,13 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>18</v>
@@ -4036,41 +3989,41 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>18</v>
+        <v>213</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>155</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>18</v>
+        <v>217</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>18</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>18</v>
@@ -4079,19 +4032,23 @@
         <v>18</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>18</v>
       </c>
@@ -4139,13 +4096,13 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>18</v>
@@ -4154,30 +4111,30 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>18</v>
+        <v>226</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>18</v>
+        <v>230</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>18</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4188,7 +4145,7 @@
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>18</v>
@@ -4197,20 +4154,18 @@
         <v>18</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4235,13 +4190,13 @@
         <v>18</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>226</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>18</v>
@@ -4259,53 +4214,53 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>18</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>232</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>234</v>
+        <v>133</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>78</v>
@@ -4320,20 +4275,18 @@
         <v>18</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>235</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>236</v>
+        <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>18</v>
       </c>
@@ -4381,10 +4334,10 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>78</v>
@@ -4393,65 +4346,69 @@
         <v>18</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>240</v>
+        <v>18</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>242</v>
+        <v>18</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>243</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>244</v>
+        <v>18</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>245</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>18</v>
       </c>
@@ -4499,25 +4456,25 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>18</v>
@@ -4534,21 +4491,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>18</v>
@@ -4560,17 +4517,15 @@
         <v>18</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>135</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4595,13 +4550,13 @@
         <v>18</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>18</v>
+        <v>248</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>18</v>
+        <v>249</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>18</v>
@@ -4619,49 +4574,49 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>18</v>
-      </c>
       <c r="AP23" t="s" s="2">
-        <v>18</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4674,13 +4629,13 @@
         <v>18</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>256</v>
@@ -4689,10 +4644,10 @@
         <v>257</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>137</v>
+        <v>258</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>143</v>
+        <v>259</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -4717,13 +4672,13 @@
         <v>18</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>18</v>
+        <v>262</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -4741,7 +4696,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4753,37 +4708,37 @@
         <v>18</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>131</v>
+        <v>263</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>18</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>18</v>
+        <v>253</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>18</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>18</v>
+        <v>266</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4799,19 +4754,23 @@
         <v>18</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
       </c>
@@ -4835,13 +4794,13 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>262</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>263</v>
+        <v>18</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
@@ -4859,7 +4818,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4874,30 +4833,30 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4908,7 +4867,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>18</v>
@@ -4920,19 +4879,17 @@
         <v>18</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -4957,13 +4914,13 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>274</v>
+        <v>18</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>275</v>
+        <v>18</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>276</v>
+        <v>18</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
@@ -4981,13 +4938,13 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>18</v>
@@ -4999,31 +4956,31 @@
         <v>18</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>278</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>280</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5039,22 +4996,20 @@
         <v>18</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5103,7 +5058,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5118,7 +5073,7 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>286</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>287</v>
@@ -5127,21 +5082,21 @@
         <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>290</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5149,7 +5104,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>
@@ -5161,18 +5116,20 @@
         <v>18</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>215</v>
+        <v>290</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>294</v>
       </c>
@@ -5223,10 +5180,10 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>88</v>
@@ -5247,10 +5204,10 @@
         <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>289</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>18</v>
@@ -5284,18 +5241,16 @@
         <v>18</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>215</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>300</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5358,30 +5313,30 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>18</v>
+        <v>301</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>302</v>
+        <v>18</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>18</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5389,10 +5344,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
@@ -5401,22 +5356,22 @@
         <v>18</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>18</v>
@@ -5465,13 +5420,13 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>18</v>
@@ -5483,27 +5438,27 @@
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>18</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5526,16 +5481,18 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>312</v>
+        <v>146</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>18</v>
       </c>
@@ -5559,13 +5516,13 @@
         <v>18</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>18</v>
+        <v>318</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>18</v>
+        <v>319</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>18</v>
@@ -5583,7 +5540,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5598,30 +5555,30 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>315</v>
+        <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>18</v>
+        <v>321</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>318</v>
+        <v>18</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>319</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5632,7 +5589,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>18</v>
@@ -5644,20 +5601,16 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O32" t="s" s="2">
         <v>324</v>
       </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>18</v>
       </c>
@@ -5705,13 +5658,13 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>18</v>
@@ -5726,24 +5679,24 @@
         <v>325</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>326</v>
+        <v>18</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>327</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5766,18 +5719,16 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>233</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>330</v>
+        <v>234</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>331</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>18</v>
       </c>
@@ -5801,13 +5752,13 @@
         <v>18</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>332</v>
+        <v>18</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>333</v>
+        <v>18</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>18</v>
@@ -5825,7 +5776,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>328</v>
+        <v>235</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5837,19 +5788,19 @@
         <v>18</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>334</v>
+        <v>236</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>335</v>
+        <v>18</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>18</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>18</v>
@@ -5860,21 +5811,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>18</v>
@@ -5886,15 +5837,17 @@
         <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>235</v>
+        <v>134</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>337</v>
+        <v>135</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>18</v>
@@ -5943,31 +5896,31 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>239</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>339</v>
+        <v>236</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>317</v>
+        <v>18</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -5978,42 +5931,46 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>18</v>
       </c>
@@ -6061,25 +6018,25 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>18</v>
@@ -6096,21 +6053,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>18</v>
@@ -6122,18 +6079,20 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>135</v>
+        <v>330</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>252</v>
+        <v>331</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>18</v>
       </c>
@@ -6181,34 +6140,34 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>253</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>250</v>
+        <v>334</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>18</v>
+        <v>335</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>18</v>
+        <v>303</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>18</v>
+        <v>336</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>18</v>
@@ -6216,45 +6175,43 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>256</v>
+        <v>338</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>143</v>
+        <v>340</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>18</v>
@@ -6279,13 +6236,13 @@
         <v>18</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>18</v>
+        <v>341</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>18</v>
+        <v>342</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>18</v>
@@ -6303,31 +6260,31 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>258</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>131</v>
+        <v>334</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>18</v>
+        <v>343</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>18</v>
+        <v>303</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>18</v>
@@ -6338,10 +6295,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6352,7 +6309,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>18</v>
@@ -6364,20 +6321,18 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O38" t="s" s="2">
         <v>347</v>
       </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>18</v>
       </c>
@@ -6401,13 +6356,13 @@
         <v>18</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>18</v>
+        <v>212</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>18</v>
@@ -6425,13 +6380,13 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>18</v>
@@ -6446,13 +6401,13 @@
         <v>348</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>18</v>
@@ -6460,10 +6415,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6471,7 +6426,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
@@ -6486,15 +6441,17 @@
         <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>108</v>
+        <v>221</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
         <v>354</v>
       </c>
@@ -6521,13 +6478,13 @@
         <v>18</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>355</v>
+        <v>18</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>18</v>
@@ -6545,10 +6502,10 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>88</v>
@@ -6563,13 +6520,13 @@
         <v>18</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6594,7 +6551,7 @@
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>18</v>
@@ -6606,17 +6563,15 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>233</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6641,13 +6596,13 @@
         <v>18</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>226</v>
+        <v>18</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>18</v>
@@ -6665,34 +6620,34 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>235</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>362</v>
+        <v>236</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>363</v>
+        <v>18</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>18</v>
@@ -6700,21 +6655,21 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>18</v>
@@ -6726,20 +6681,18 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>235</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>365</v>
+        <v>135</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>366</v>
+        <v>238</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>18</v>
       </c>
@@ -6787,31 +6740,31 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>239</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>369</v>
+        <v>236</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>370</v>
+        <v>18</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>371</v>
+        <v>18</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -6822,42 +6775,46 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>18</v>
       </c>
@@ -6905,25 +6862,25 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>18</v>
@@ -6940,21 +6897,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>18</v>
@@ -6966,18 +6923,18 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>135</v>
+        <v>362</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>18</v>
       </c>
@@ -7025,31 +6982,31 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>253</v>
+        <v>361</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>250</v>
+        <v>365</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>18</v>
+        <v>366</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>18</v>
+        <v>357</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -7060,45 +7017,43 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>255</v>
+        <v>368</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>256</v>
+        <v>369</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>143</v>
+        <v>371</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -7147,31 +7102,31 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>258</v>
+        <v>367</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>131</v>
+        <v>273</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>18</v>
+        <v>372</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>18</v>
+        <v>357</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7182,10 +7137,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7196,7 +7151,7 @@
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>18</v>
@@ -7208,17 +7163,17 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>146</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>18</v>
@@ -7243,13 +7198,13 @@
         <v>18</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>18</v>
+        <v>377</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>18</v>
+        <v>378</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>18</v>
@@ -7267,13 +7222,13 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>18</v>
@@ -7291,7 +7246,7 @@
         <v>380</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7313,10 +7268,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>18</v>
@@ -7325,10 +7280,10 @@
         <v>18</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>383</v>
@@ -7336,9 +7291,11 @@
       <c r="M46" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N46" s="2"/>
+      <c r="N46" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>18</v>
@@ -7390,42 +7347,42 @@
         <v>381</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>387</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>287</v>
+        <v>388</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>371</v>
+        <v>155</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>18</v>
+        <v>391</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7436,7 +7393,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>18</v>
@@ -7448,18 +7405,16 @@
         <v>18</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>233</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
+        <v>234</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>390</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>18</v>
       </c>
@@ -7483,13 +7438,13 @@
         <v>18</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>391</v>
+        <v>18</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>392</v>
+        <v>18</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>18</v>
@@ -7507,31 +7462,31 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>387</v>
+        <v>235</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>393</v>
+        <v>236</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>394</v>
+        <v>18</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>371</v>
+        <v>18</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>18</v>
@@ -7542,14 +7497,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>396</v>
+        <v>133</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7568,20 +7523,18 @@
         <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>235</v>
+        <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>397</v>
+        <v>135</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>398</v>
+        <v>238</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>18</v>
       </c>
@@ -7629,7 +7582,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>395</v>
+        <v>239</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7641,65 +7594,69 @@
         <v>18</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>401</v>
+        <v>139</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>402</v>
+        <v>236</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>403</v>
+        <v>18</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>405</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
       </c>
@@ -7747,25 +7704,25 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>18</v>
@@ -7782,21 +7739,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>18</v>
@@ -7805,20 +7762,18 @@
         <v>18</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>134</v>
+        <v>396</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>135</v>
+        <v>397</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>18</v>
@@ -7867,80 +7822,80 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>253</v>
+        <v>395</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>18</v>
+        <v>399</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>18</v>
+        <v>400</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>256</v>
+        <v>402</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>257</v>
+        <v>403</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>137</v>
+        <v>404</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>143</v>
+        <v>405</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -7965,13 +7920,13 @@
         <v>18</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>18</v>
+        <v>406</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>18</v>
+        <v>407</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>18</v>
@@ -7989,45 +7944,45 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>258</v>
+        <v>401</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>131</v>
+        <v>408</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>18</v>
+        <v>409</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>18</v>
+        <v>155</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>18</v>
+        <v>410</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>18</v>
+        <v>411</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8047,19 +8002,21 @@
         <v>18</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>410</v>
+        <v>146</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>18</v>
       </c>
@@ -8083,13 +8040,13 @@
         <v>18</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>18</v>
+        <v>416</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>18</v>
+        <v>417</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>18</v>
@@ -8107,7 +8064,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8125,27 +8082,27 @@
         <v>18</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>287</v>
+        <v>418</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>155</v>
+        <v>420</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>18</v>
+        <v>421</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>414</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8171,16 +8128,16 @@
         <v>146</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>18</v>
@@ -8205,13 +8162,13 @@
         <v>18</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>162</v>
+        <v>210</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>18</v>
@@ -8229,7 +8186,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8247,27 +8204,27 @@
         <v>18</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>155</v>
+        <v>420</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8278,7 +8235,7 @@
         <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>18</v>
@@ -8293,14 +8250,16 @@
         <v>146</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>18</v>
@@ -8325,37 +8284,37 @@
         <v>18</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>162</v>
+        <v>210</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="Z54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AA54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>426</v>
-      </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>18</v>
@@ -8367,16 +8326,16 @@
         <v>18</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>435</v>
+        <v>18</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>18</v>
@@ -8384,10 +8343,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8407,22 +8366,22 @@
         <v>18</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>18</v>
@@ -8447,13 +8406,13 @@
         <v>18</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>438</v>
+        <v>18</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>441</v>
+        <v>18</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>18</v>
@@ -8471,7 +8430,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8480,7 +8439,7 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>18</v>
+        <v>445</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>100</v>
@@ -8489,27 +8448,27 @@
         <v>18</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>444</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8520,7 +8479,7 @@
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>18</v>
@@ -8532,19 +8491,17 @@
         <v>18</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
@@ -8569,13 +8526,13 @@
         <v>18</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>162</v>
+        <v>18</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>450</v>
+        <v>18</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>451</v>
+        <v>18</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>18</v>
@@ -8593,13 +8550,13 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>18</v>
@@ -8617,7 +8574,7 @@
         <v>453</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>18</v>
@@ -8654,19 +8611,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>215</v>
+        <v>455</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8724,7 +8681,7 @@
         <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>100</v>
@@ -8739,10 +8696,10 @@
         <v>461</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>462</v>
+        <v>18</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>18</v>
@@ -8750,10 +8707,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8764,7 +8721,7 @@
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>18</v>
@@ -8776,17 +8733,17 @@
         <v>18</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -8835,13 +8792,13 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>18</v>
@@ -8859,7 +8816,7 @@
         <v>467</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>18</v>
@@ -8893,23 +8850,19 @@
         <v>18</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>469</v>
+        <v>200</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>470</v>
+        <v>233</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>18</v>
       </c>
@@ -8957,7 +8910,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>468</v>
+        <v>235</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8966,22 +8919,22 @@
         <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>459</v>
+        <v>18</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>474</v>
+        <v>236</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>475</v>
+        <v>18</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -8992,14 +8945,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9018,18 +8971,18 @@
         <v>18</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>235</v>
+        <v>134</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>477</v>
+        <v>135</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>479</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>18</v>
       </c>
@@ -9077,7 +9030,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>476</v>
+        <v>239</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -9089,19 +9042,19 @@
         <v>18</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>480</v>
+        <v>236</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>481</v>
+        <v>18</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>18</v>
@@ -9112,42 +9065,46 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>18</v>
+        <v>241</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>18</v>
       </c>
@@ -9195,25 +9152,25 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>18</v>
@@ -9230,21 +9187,21 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>18</v>
@@ -9256,17 +9213,15 @@
         <v>18</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>135</v>
+        <v>472</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>18</v>
@@ -9315,31 +9270,31 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>253</v>
+        <v>471</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>250</v>
+        <v>379</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>18</v>
+        <v>474</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>18</v>
+        <v>420</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9350,45 +9305,45 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>134</v>
+        <v>476</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>256</v>
+        <v>477</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>257</v>
+        <v>478</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>137</v>
+        <v>479</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>143</v>
+        <v>480</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>18</v>
@@ -9437,276 +9392,36 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>258</v>
+        <v>475</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>131</v>
+        <v>481</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>18</v>
+        <v>482</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>18</v>
+        <v>420</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP65" t="s" s="2">
         <v>18</v>
       </c>
     </row>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T18:07:37+00:00</t>
+    <t>2026-05-16T09:46:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fhirpot-audit-event.xlsx
+++ b/StructureDefinition-fhirpot-audit-event.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.12</t>
+    <t>0.0.13</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T09:46:24+00:00</t>
+    <t>2026-05-16T09:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
